--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -18544,16 +18544,16 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O110" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3305530637567811</v>
+        <v>0.3342258755763009</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21064,16 +21064,16 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21756,16 +21756,16 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22300,16 +22300,16 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.03476553957149517</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444711</v>
+        <v>444722</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -16968,16 +16968,16 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O98" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.1542580964198312</v>
+        <v>0.157930908239351</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -20032,16 +20032,16 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="O116" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3452443110348603</v>
+        <v>0.2754608864639843</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22552,16 +22552,16 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.01836405909759895</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23244,16 +23244,16 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23788,16 +23788,16 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.03476553957149517</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23866,6 +23866,154 @@
       <c r="BC138" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>3</v>
+      </c>
+      <c r="O139" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23902,7 +24050,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -23985,7 +24133,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -23995,7 +24143,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -24047,7 +24195,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444726</v>
+        <v>444709</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>7</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -1753,9 +1747,6 @@
       <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01162781954275227</v>
       </c>
@@ -2049,9 +2037,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -2694,7 +2679,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2841,9 +2826,6 @@
       <c r="O14" t="n">
         <v>9</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.08410392385455011</v>
       </c>
@@ -4273,9 +4255,6 @@
       <c r="O23" t="n">
         <v>11</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -4569,9 +4548,6 @@
       <c r="O25" t="n">
         <v>7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -4965,9 +4941,6 @@
       <c r="O27" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -5113,9 +5086,6 @@
       <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01162781954275227</v>
       </c>
@@ -5261,9 +5231,6 @@
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -5906,7 +5873,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6053,9 +6020,6 @@
       <c r="O33" t="n">
         <v>9</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.08410392385455011</v>
       </c>
@@ -7485,9 +7449,6 @@
       <c r="O42" t="n">
         <v>12</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -7781,9 +7742,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -8177,9 +8135,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8325,9 +8280,6 @@
       <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -8473,9 +8425,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -9118,7 +9067,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -9265,9 +9214,6 @@
       <c r="O52" t="n">
         <v>15</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.1401732064242502</v>
       </c>
@@ -10401,9 +10347,6 @@
       <c r="O59" t="n">
         <v>67</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.246078391907826</v>
       </c>
@@ -10549,9 +10492,6 @@
       <c r="O60" t="n">
         <v>93278</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>43.67710964125839</v>
       </c>
@@ -10697,9 +10637,6 @@
       <c r="O61" t="n">
         <v>14</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -10993,9 +10930,6 @@
       <c r="O63" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -11389,9 +11323,6 @@
       <c r="O65" t="n">
         <v>7</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -11537,9 +11468,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -11685,9 +11613,6 @@
       <c r="O67" t="n">
         <v>9</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -12081,9 +12006,6 @@
       <c r="O69" t="n">
         <v>36</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.6808537679298584</v>
       </c>
@@ -12330,7 +12252,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -12477,9 +12399,6 @@
       <c r="O71" t="n">
         <v>29</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.271001532420217</v>
       </c>
@@ -12873,9 +12792,6 @@
       <c r="O73" t="n">
         <v>21</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.09125954137517482</v>
       </c>
@@ -13613,9 +13529,6 @@
       <c r="O78" t="n">
         <v>53</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1946590264345489</v>
       </c>
@@ -13761,9 +13674,6 @@
       <c r="O79" t="n">
         <v>82988</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>38.85885176471141</v>
       </c>
@@ -13909,9 +13819,6 @@
       <c r="O80" t="n">
         <v>17</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -14205,9 +14112,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14601,9 +14505,6 @@
       <c r="O84" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -14749,9 +14650,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -14897,9 +14795,6 @@
       <c r="O86" t="n">
         <v>7</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1238283078056854</v>
       </c>
@@ -15293,9 +15188,6 @@
       <c r="O88" t="n">
         <v>15</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.2836890699707744</v>
       </c>
@@ -15542,7 +15434,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -15689,9 +15581,6 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -16085,9 +15974,6 @@
       <c r="O92" t="n">
         <v>16</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -16973,9 +16859,6 @@
       <c r="O98" t="n">
         <v>43</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.157930908239351</v>
       </c>
@@ -17121,9 +17004,6 @@
       <c r="O99" t="n">
         <v>59160</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>27.70147094038087</v>
       </c>
@@ -17417,9 +17297,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -17813,9 +17690,6 @@
       <c r="O103" t="n">
         <v>3</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -17961,9 +17835,6 @@
       <c r="O104" t="n">
         <v>8</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.01550375939033637</v>
       </c>
@@ -18109,9 +17980,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18505,9 +18373,6 @@
       <c r="O107" t="n">
         <v>11</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.2080386513119012</v>
       </c>
@@ -18754,7 +18619,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -18901,9 +18766,6 @@
       <c r="O109" t="n">
         <v>5</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -19297,9 +19159,6 @@
       <c r="O111" t="n">
         <v>22</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -19445,9 +19304,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19593,9 +19449,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19741,9 +19594,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19889,9 +19739,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -20037,9 +19884,6 @@
       <c r="O116" t="n">
         <v>75</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.2754608864639843</v>
       </c>
@@ -20185,9 +20029,6 @@
       <c r="O117" t="n">
         <v>40053</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>18.75468248098504</v>
       </c>
@@ -20333,9 +20174,6 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -20729,9 +20567,6 @@
       <c r="O120" t="n">
         <v>6</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.01162781954275227</v>
       </c>
@@ -20877,9 +20712,6 @@
       <c r="O121" t="n">
         <v>8</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -21273,9 +21105,6 @@
       <c r="O123" t="n">
         <v>6</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -21669,9 +21498,6 @@
       <c r="O125" t="n">
         <v>34</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.1477535431788545</v>
       </c>
@@ -21817,9 +21643,6 @@
       <c r="O126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -21965,9 +21788,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -22113,9 +21933,6 @@
       <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -22261,9 +22078,6 @@
       <c r="O129" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -22409,9 +22223,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -22557,9 +22368,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22705,9 +22513,6 @@
       <c r="O132" t="n">
         <v>101</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.04729291015852717</v>
       </c>
@@ -22853,9 +22658,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23244,16 +23046,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O135" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R135" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23392,16 +23191,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R136" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23554,10 +23350,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -23788,16 +23584,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R138" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23940,9 +23733,6 @@
       </c>
       <c r="O139" t="n">
         <v>3</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0.002450425222697299</v>
@@ -24195,7 +23985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444709</v>
+        <v>444717</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -23584,13 +23584,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R138" t="n">
-        <v>0.04345692446436896</v>
+        <v>0.04780261691080586</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444717</v>
+        <v>444718</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -19879,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O116" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="R116" t="n">
-        <v>0.2754608864639843</v>
+        <v>0.367281181951979</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22653,13 +22653,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22812,10 +22812,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444718</v>
+        <v>444749</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R131" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444749</v>
+        <v>444751</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -23584,13 +23584,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R138" t="n">
-        <v>0.04780261691080586</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444751</v>
+        <v>444752</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -19879,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O116" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R116" t="n">
-        <v>0.367281181951979</v>
+        <v>0.3709539937714988</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R131" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23046,13 +23046,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R135" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23802,6 +23802,151 @@
         </is>
       </c>
       <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>8</v>
+      </c>
+      <c r="O140" t="n">
+        <v>8</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23840,7 +23985,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -23923,7 +24068,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -23933,7 +24078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -23985,7 +24130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444752</v>
+        <v>444766</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -20130,12 +20130,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20169,95 +20169,84 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>1120</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>1120</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07926879695771397</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20273,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -20333,98 +20322,23 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
+      <c r="R119" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -20518,17 +20432,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20562,81 +20476,170 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
-        <v>6</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.01162781954275227</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20668,12 +20671,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20707,95 +20710,81 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R121" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20822,7 +20811,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -20871,98 +20860,23 @@
       <c r="O122" t="n">
         <v>8</v>
       </c>
+      <c r="R122" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -21056,17 +20970,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21100,22 +21014,39 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.05606928256970008</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21123,6 +21054,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21140,7 +21129,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21153,42 +21142,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21215,7 +21204,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -21264,98 +21253,23 @@
       <c r="O124" t="n">
         <v>6</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DENGUE</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -21449,17 +21363,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21493,81 +21407,170 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="O125" t="n">
-        <v>34</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.1477535431788545</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21599,12 +21602,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21629,7 +21632,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21638,13 +21641,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R126" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.1477535431788545</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -21677,42 +21680,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21777,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21919,7 +21922,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21928,13 +21931,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22064,7 +22067,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22073,13 +22076,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R129" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22209,7 +22212,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22218,13 +22221,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22324,12 +22327,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22354,22 +22357,22 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.02938249455615832</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22402,42 +22405,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22469,12 +22472,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22508,13 +22511,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="O132" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="R132" t="n">
-        <v>0.04729291015852717</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22547,42 +22550,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22617,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22653,95 +22656,81 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="R133" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.04729291015852717</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22757,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -22817,98 +22806,23 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -23002,17 +22916,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23046,81 +22960,170 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>10</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0.01937969923792046</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23152,12 +23155,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23191,95 +23194,81 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O136" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23295,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -23355,98 +23344,23 @@
       <c r="O137" t="n">
         <v>6</v>
       </c>
+      <c r="R137" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -23540,17 +23454,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23584,81 +23498,170 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O138" t="n">
-        <v>12</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0.05214830935724275</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23690,12 +23693,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23720,7 +23723,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23729,13 +23732,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R139" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23768,42 +23771,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23865,7 +23868,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23874,13 +23877,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O140" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R140" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23947,6 +23950,151 @@
         </is>
       </c>
       <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>8</v>
+      </c>
+      <c r="O141" t="n">
+        <v>8</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24068,7 +24216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -24078,7 +24226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -24130,7 +24278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444766</v>
+        <v>445886</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -19879,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O116" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3709539937714988</v>
+        <v>0.3782996174105384</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22511,13 +22511,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O132" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="R132" t="n">
-        <v>0.02938249455615832</v>
+        <v>0.08814748366847497</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23339,13 +23339,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R137" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23498,10 +23498,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>445886</v>
+        <v>445907</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -16854,13 +16854,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O98" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="R98" t="n">
-        <v>0.157930908239351</v>
+        <v>0.2020046500735885</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19879,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O116" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3782996174105384</v>
+        <v>0.3819724292300582</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22511,13 +22511,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O132" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R132" t="n">
-        <v>0.08814748366847497</v>
+        <v>0.09916591912703433</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>445907</v>
+        <v>445923</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -16999,13 +16999,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>59160</v>
+        <v>54138</v>
       </c>
       <c r="O99" t="n">
-        <v>59160</v>
+        <v>54138</v>
       </c>
       <c r="R99" t="n">
-        <v>27.70147094038087</v>
+        <v>25.34993633824103</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -20024,13 +20024,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>40053</v>
+        <v>46395</v>
       </c>
       <c r="O117" t="n">
-        <v>40053</v>
+        <v>46395</v>
       </c>
       <c r="R117" t="n">
-        <v>18.75468248098504</v>
+        <v>21.72430264163236</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -22656,13 +22656,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>101</v>
+        <v>18558</v>
       </c>
       <c r="O133" t="n">
-        <v>101</v>
+        <v>18558</v>
       </c>
       <c r="R133" t="n">
-        <v>0.04729291015852717</v>
+        <v>8.689721056652942</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>445923</v>
+        <v>465700</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -19879,13 +19879,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O116" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3819724292300582</v>
+        <v>0.385645241049578</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22511,13 +22511,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O132" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="R132" t="n">
-        <v>0.09916591912703433</v>
+        <v>0.06243780093183643</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>465700</v>
+        <v>465691</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -16999,13 +16999,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>54138</v>
+        <v>53049</v>
       </c>
       <c r="O99" t="n">
-        <v>54138</v>
+        <v>53049</v>
       </c>
       <c r="R99" t="n">
-        <v>25.34993633824103</v>
+        <v>24.84001575247235</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -18368,13 +18368,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R107" t="n">
-        <v>0.2080386513119012</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -18527,10 +18527,10 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -20024,13 +20024,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>46395</v>
+        <v>44692</v>
       </c>
       <c r="O117" t="n">
-        <v>46395</v>
+        <v>44692</v>
       </c>
       <c r="R117" t="n">
-        <v>21.72430264163236</v>
+        <v>20.92687862183066</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21248,13 +21248,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R124" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21301,42 +21301,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21368,12 +21368,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21407,29 +21407,29 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>Denguefeber</t>
+          <t>Dengue fever</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -21489,17 +21489,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly dengue notifications.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -21535,42 +21535,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21602,12 +21602,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21641,81 +21641,95 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="O126" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="R126" t="n">
-        <v>0.1477535431788545</v>
+        <v>0.05606928256970008</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21742,17 +21756,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21777,7 +21791,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21786,81 +21800,170 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21892,12 +21995,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21922,7 +22025,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21931,13 +22034,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R128" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.1477535431788545</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21970,42 +22073,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22067,7 +22170,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22076,13 +22179,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22212,7 +22315,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22357,7 +22460,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22366,13 +22469,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22472,12 +22575,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22502,22 +22605,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>0.06243780093183643</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22550,42 +22653,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22617,12 +22720,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22647,22 +22750,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>18558</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>18558</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>8.689721056652942</v>
+        <v>0</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22695,42 +22798,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22762,12 +22865,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22801,95 +22904,81 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R134" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.06611061275135623</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22916,17 +23005,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22960,170 +23049,81 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>28051</v>
       </c>
       <c r="O135" t="n">
-        <v>1</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
+        <v>28051</v>
+      </c>
+      <c r="R135" t="n">
+        <v>13.13478636491926</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -23155,12 +23155,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23194,81 +23194,95 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R136" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23295,17 +23309,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23339,22 +23353,39 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O137" t="n">
-        <v>9</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.1592078243215956</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -23362,6 +23393,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23374,12 +23463,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -23387,47 +23476,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23454,17 +23543,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23498,170 +23587,81 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O138" t="n">
-        <v>9</v>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.02906954885688069</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23693,12 +23693,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23732,81 +23732,95 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R139" t="n">
-        <v>0.05214830935724275</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23833,17 +23847,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23868,7 +23882,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23877,81 +23891,170 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
-        <v>3</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23983,12 +24086,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24013,7 +24116,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24022,13 +24125,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O141" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R141" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24061,40 +24164,475 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>3</v>
+      </c>
+      <c r="O142" t="n">
+        <v>3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW141" t="inlineStr">
+      <c r="AW142" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
+      <c r="AX142" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
+      <c r="AY142" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA141" t="inlineStr">
+      <c r="BA142" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB141" t="inlineStr">
+      <c r="BB142" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC141" t="inlineStr">
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>8</v>
+      </c>
+      <c r="O143" t="n">
+        <v>8</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
+        <v>7</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24133,7 +24671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -24216,7 +24754,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -24226,7 +24764,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -24246,7 +24784,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -24278,7 +24816,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>465691</v>
+        <v>472416</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -37077,12 +37077,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -37116,13 +37116,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R199" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.04065810840590128</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -37155,42 +37155,42 @@
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37222,12 +37222,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37261,95 +37261,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O200" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R200" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37376,7 +37362,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -37425,98 +37411,23 @@
       <c r="O201" t="n">
         <v>8</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37610,17 +37521,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37654,22 +37565,39 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O202" t="n">
-        <v>10</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.1891260466471829</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -37677,6 +37605,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37694,7 +37680,7 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -37707,42 +37693,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37769,7 +37755,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -37818,98 +37804,23 @@
       <c r="O203" t="n">
         <v>10</v>
       </c>
+      <c r="R203" t="n">
+        <v>0.1891260466471829</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Dengue fever</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly dengue notifications.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -38003,17 +37914,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38047,22 +37958,39 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O204" t="n">
-        <v>6</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.05606928256970008</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Dengue fever</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -38070,6 +37998,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly dengue notifications.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38087,7 +38073,7 @@
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
@@ -38100,42 +38086,42 @@
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38162,7 +38148,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -38211,98 +38197,23 @@
       <c r="O205" t="n">
         <v>6</v>
       </c>
+      <c r="R205" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DENGUE</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -38396,17 +38307,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38440,81 +38351,170 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="O206" t="n">
-        <v>34</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.1477535431788545</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38546,12 +38546,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38576,7 +38576,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -38585,13 +38585,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="O207" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R207" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.1477535431788545</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -38624,42 +38624,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38691,12 +38691,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38721,7 +38721,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -38730,93 +38730,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="O208" t="n">
-        <v>116</v>
-      </c>
-      <c r="P208" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="R208" t="n">
-        <v>1.964188275912575</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38843,7 +38831,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -38895,98 +38883,18 @@
       <c r="P209" t="n">
         <v>116</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R209" t="n">
+        <v>1.964188275912575</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -39124,22 +39032,22 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="O210" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="P210" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -39149,7 +39057,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -39184,7 +39092,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -39223,7 +39131,7 @@
         </is>
       </c>
       <c r="AN210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -39317,17 +39225,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39352,7 +39260,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -39366,76 +39274,168 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="R211" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P211" t="n">
+        <v>2</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>0</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39467,12 +39467,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39497,7 +39497,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -39506,93 +39506,81 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="O212" t="n">
-        <v>119</v>
-      </c>
-      <c r="P212" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="R212" t="n">
-        <v>2.014986248565486</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39619,7 +39607,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -39671,98 +39659,18 @@
       <c r="P213" t="n">
         <v>119</v>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R213" t="n">
+        <v>2.014986248565486</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -39900,106 +39808,106 @@
         </is>
       </c>
       <c r="N214" t="n">
+        <v>119</v>
+      </c>
+      <c r="O214" t="n">
+        <v>119</v>
+      </c>
+      <c r="P214" t="n">
+        <v>119</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
         <v>1</v>
-      </c>
-      <c r="O214" t="n">
-        <v>1</v>
-      </c>
-      <c r="P214" t="n">
-        <v>1</v>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>0</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -40093,17 +40001,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40128,7 +40036,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -40137,81 +40045,173 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O215" t="n">
-        <v>3</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P215" t="n">
+        <v>1</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>0</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40243,12 +40243,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40273,7 +40273,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -40282,93 +40282,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="O216" t="n">
-        <v>121</v>
-      </c>
-      <c r="P216" t="n">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="R216" t="n">
-        <v>2.048851563667427</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40395,7 +40383,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -40447,98 +40435,18 @@
       <c r="P217" t="n">
         <v>121</v>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R217" t="n">
+        <v>2.048851563667427</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -40676,106 +40584,106 @@
         </is>
       </c>
       <c r="N218" t="n">
+        <v>121</v>
+      </c>
+      <c r="O218" t="n">
+        <v>121</v>
+      </c>
+      <c r="P218" t="n">
+        <v>121</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
         <v>1</v>
-      </c>
-      <c r="O218" t="n">
-        <v>1</v>
-      </c>
-      <c r="P218" t="n">
-        <v>1</v>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN218" t="b">
-        <v>0</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -40869,17 +40777,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -40904,7 +40812,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -40913,81 +40821,173 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O219" t="n">
-        <v>2</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P219" t="n">
+        <v>1</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>0</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41049,7 +41049,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -41058,13 +41058,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -41164,12 +41164,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -41203,93 +41203,81 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>118</v>
-      </c>
-      <c r="P221" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>1.998053591014516</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41316,7 +41304,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -41368,98 +41356,18 @@
       <c r="P222" t="n">
         <v>118</v>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R222" t="n">
+        <v>1.998053591014516</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
@@ -41597,106 +41505,106 @@
         </is>
       </c>
       <c r="N223" t="n">
+        <v>118</v>
+      </c>
+      <c r="O223" t="n">
+        <v>118</v>
+      </c>
+      <c r="P223" t="n">
+        <v>118</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
         <v>1</v>
-      </c>
-      <c r="O223" t="n">
-        <v>1</v>
-      </c>
-      <c r="P223" t="n">
-        <v>1</v>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>0</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -41790,17 +41698,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -41825,90 +41733,182 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N224" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>18</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.06611061275135623</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>0</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT224" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41940,12 +41940,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -41979,13 +41979,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>28051</v>
+        <v>30</v>
       </c>
       <c r="O225" t="n">
-        <v>28051</v>
+        <v>30</v>
       </c>
       <c r="R225" t="n">
-        <v>13.13478636491926</v>
+        <v>0.1101843545855937</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -42018,42 +42018,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42085,12 +42085,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42124,95 +42124,81 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>2</v>
+        <v>28051</v>
       </c>
       <c r="O226" t="n">
-        <v>2</v>
+        <v>28051</v>
       </c>
       <c r="R226" t="n">
-        <v>0.03557618341728275</v>
+        <v>13.13478636491926</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -42239,7 +42225,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -42288,98 +42274,23 @@
       <c r="O227" t="n">
         <v>2</v>
       </c>
+      <c r="R227" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -42473,17 +42384,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42517,81 +42428,170 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O228" t="n">
-        <v>15</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.02906954885688069</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42623,12 +42623,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -42662,95 +42662,81 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O229" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R229" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42777,7 +42763,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -42826,98 +42812,23 @@
       <c r="O230" t="n">
         <v>10</v>
       </c>
+      <c r="R230" t="n">
+        <v>0.1768975825795506</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U230" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -43011,17 +42922,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -43055,81 +42966,170 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O231" t="n">
-        <v>12</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0.05214830935724275</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43161,12 +43161,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43191,7 +43191,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -43200,13 +43200,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O232" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R232" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -43239,42 +43239,42 @@
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43306,12 +43306,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -43345,93 +43345,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O233" t="n">
-        <v>100</v>
-      </c>
-      <c r="P233" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="R233" t="n">
-        <v>1.693265755097047</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43458,7 +43446,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -43510,98 +43498,18 @@
       <c r="P234" t="n">
         <v>100</v>
       </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R234" t="n">
+        <v>1.693265755097047</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -43739,106 +43647,106 @@
         </is>
       </c>
       <c r="N235" t="n">
+        <v>100</v>
+      </c>
+      <c r="O235" t="n">
+        <v>100</v>
+      </c>
+      <c r="P235" t="n">
+        <v>100</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
         <v>1</v>
-      </c>
-      <c r="O235" t="n">
-        <v>1</v>
-      </c>
-      <c r="P235" t="n">
-        <v>1</v>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>0</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -43932,17 +43840,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -43967,7 +43875,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -43976,81 +43884,173 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>8</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>0</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44082,12 +44082,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44121,93 +44121,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="O237" t="n">
-        <v>93</v>
-      </c>
-      <c r="P237" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="R237" t="n">
-        <v>1.574737152240254</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44234,7 +44222,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -44286,98 +44274,18 @@
       <c r="P238" t="n">
         <v>93</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R238" t="n">
+        <v>1.574737152240254</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -44515,22 +44423,22 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="O239" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="P239" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
@@ -44540,7 +44448,7 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -44575,7 +44483,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -44614,7 +44522,7 @@
         </is>
       </c>
       <c r="AN239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
@@ -44708,17 +44616,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44743,7 +44651,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -44752,81 +44660,173 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O240" t="n">
-        <v>7</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P240" t="n">
+        <v>2</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>0</v>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44858,12 +44858,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -44897,93 +44897,81 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="O241" t="n">
-        <v>103</v>
-      </c>
-      <c r="P241" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="R241" t="n">
-        <v>1.744063727749959</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45010,7 +44998,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -45062,98 +45050,18 @@
       <c r="P242" t="n">
         <v>103</v>
       </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R242" t="n">
+        <v>1.744063727749959</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
@@ -45291,106 +45199,106 @@
         </is>
       </c>
       <c r="N243" t="n">
+        <v>103</v>
+      </c>
+      <c r="O243" t="n">
+        <v>103</v>
+      </c>
+      <c r="P243" t="n">
+        <v>103</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
         <v>1</v>
-      </c>
-      <c r="O243" t="n">
-        <v>1</v>
-      </c>
-      <c r="P243" t="n">
-        <v>1</v>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>0</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -45456,6 +45364,243 @@
         </is>
       </c>
       <c r="BC243" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1</v>
+      </c>
+      <c r="P244" t="n">
+        <v>1</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -45577,7 +45722,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -45587,7 +45732,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -45639,7 +45784,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474485</v>
+        <v>474501</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -57239,13 +57239,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O304" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R304" t="n">
-        <v>0.3893180528690977</v>
+        <v>0.3929908646886175</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O358" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R358" t="n">
-        <v>0.1285484136831927</v>
+        <v>0.1616037200588708</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -68321,13 +68321,13 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R367" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
@@ -68485,10 +68485,10 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U368" t="inlineStr">
         <is>
@@ -73728,7 +73728,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482777</v>
+        <v>482788</v>
       </c>
     </row>
     <row r="16">
